--- a/diseases/d145/2000-2004.xlsx
+++ b/diseases/d145/2000-2004.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +8120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8028,6 +8273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8176,6 +8426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8324,6 +8579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8732,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8620,6 +8885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8768,6 +9038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8916,6 +9191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9064,6 +9344,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9360,6 +9650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9506,6 +9801,11 @@
       <c r="S61" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">

--- a/diseases/d145/2000-2004.xlsx
+++ b/diseases/d145/2000-2004.xlsx
@@ -5233,17 +5233,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DE-BB</t>
+          <t>DE-NW</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Brandenburg, Germany</t>
+          <t>Nordrhein-Westfalen, Germany</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5282,121 +5282,47 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>country:DE-BB:national</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN31" t="b">
-        <v>0</v>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
         <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -5468,12 +5394,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DE-BE</t>
+          <t>DE-NW</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Nordrhein-Westfalen, Germany</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5554,12 +5480,12 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>country:DE-BE:national</t>
+          <t>country:DE-NW:national</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
@@ -5603,30 +5529,34 @@
         </is>
       </c>
       <c r="AN32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
         <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -5693,17 +5623,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DE-BW</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Baden-Württemberg, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5728,175 +5658,98 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>country:DE-BW:national</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN33" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5923,17 +5776,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5958,175 +5811,98 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>country:DE-BY:national</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN34" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6153,17 +5929,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>DE-HB</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bremen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6188,175 +5964,98 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:DE-HB:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6383,17 +6082,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6418,175 +6117,98 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>country:DE-HE:national</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN36" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6613,17 +6235,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>DE-HH</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hamburg, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6648,175 +6270,98 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>country:DE-HH:national</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN37" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6843,17 +6388,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>DE-MV</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Mecklenburg-Vorpommern, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6878,175 +6423,98 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>country:DE-MV:national</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN38" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7073,17 +6541,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DE-NI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Niedersachsen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -7108,175 +6576,98 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>country:DE-NI:national</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN39" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7303,17 +6694,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DE-NW</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -7338,175 +6729,98 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>country:DE-NW:national</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN40" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7533,17 +6847,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DE-RP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7568,175 +6882,98 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>country:DE-RP:national</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN41" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7763,17 +7000,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DE-SH</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7798,175 +7035,98 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>country:DE-SH:national</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN42" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7993,17 +7153,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DE-SL</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Saarland, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -8028,175 +7188,98 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>country:DE-SL:national</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN43" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8223,17 +7306,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -8258,175 +7341,98 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>country:DE-SN:national</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN44" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8453,17 +7459,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>DE-ST</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -8488,175 +7494,98 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>country:DE-ST:national</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN45" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8683,17 +7612,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>DE-TH</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Thüringen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -8718,175 +7647,98 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>country:DE-TH:national</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN46" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8948,12 +7800,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -9101,12 +7953,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -9254,12 +8106,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -9407,12 +8259,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -9560,12 +8412,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -9713,12 +8565,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -9866,12 +8718,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -10019,12 +8871,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -10172,12 +9024,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -10325,12 +9177,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -10478,12 +9330,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -10631,12 +9483,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -10749,17 +9601,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -10784,98 +9636,178 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2004-06-07</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
+        <v>0</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -10907,12 +9839,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -10937,98 +9869,101 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2004-06-07</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11055,17 +9990,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -11090,98 +10025,179 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2004-06-07</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>l-user-ckfallfieber</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Läuserückfallfieber</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>country:DE-BY:national</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN61" t="b">
+        <v>1</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11243,12 +10259,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -11396,12 +10412,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -11549,12 +10565,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -11702,12 +10718,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2004-10-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -11855,12 +10871,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -12008,12 +11024,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-12-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2004-12</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -12098,5602 +11114,6 @@
         </is>
       </c>
       <c r="BC67" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>2004-02-01</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>2004-02</t>
-        </is>
-      </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP68" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
-      <c r="AT68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV68" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA68" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB68" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC68" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>2004-03-01</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>2004-03</t>
-        </is>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP69" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr"/>
-      <c r="AT69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV69" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA69" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB69" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC69" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>2004-04-01</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>2004-04</t>
-        </is>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP70" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
-      <c r="AT70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV70" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA70" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB70" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC70" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>2004-05-01</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>2004-05</t>
-        </is>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP71" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
-      <c r="AT71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV71" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA71" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB71" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC71" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>2004-06-01</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP72" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
-      <c r="AT72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV72" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA72" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB72" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC72" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N73" t="n">
-        <v>1</v>
-      </c>
-      <c r="O73" t="n">
-        <v>1</v>
-      </c>
-      <c r="P73" t="n">
-        <v>1</v>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG73" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP73" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
-      <c r="AT73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV73" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>official_webforms_csv_export</t>
-        </is>
-      </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA73" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB73" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="BC73" t="inlineStr">
-        <is>
-          <t>official_webforms_csv_export</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>DE-BB</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Brandenburg, Germany</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N74" t="n">
-        <v>1</v>
-      </c>
-      <c r="O74" t="n">
-        <v>1</v>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>country:DE-BB:national</t>
-        </is>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG74" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL74" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP74" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
-      <c r="AT74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV74" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA74" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB74" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC74" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>DE-BE</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>1</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1</v>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>country:DE-BE:national</t>
-        </is>
-      </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL75" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP75" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
-      <c r="AT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV75" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA75" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB75" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC75" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>DE-BW</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Baden-Württemberg, Germany</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N76" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1</v>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>country:DE-BW:national</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL76" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP76" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
-      <c r="AT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV76" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA76" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB76" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC76" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>DE-BY</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Bayern, Germany</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N77" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1</v>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>country:DE-BY:national</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL77" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP77" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
-      <c r="AT77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV77" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA77" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB77" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC77" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>DE-HB</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Bremen, Germany</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
-        <v>1</v>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>country:DE-HB:national</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG78" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL78" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP78" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
-      <c r="AT78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV78" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA78" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB78" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC78" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>DE-HE</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Hessen, Germany</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N79" t="n">
-        <v>1</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>country:DE-HE:national</t>
-        </is>
-      </c>
-      <c r="AD79" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG79" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL79" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP79" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
-      <c r="AT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV79" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA79" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB79" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC79" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>DE-HH</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Hamburg, Germany</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N80" t="n">
-        <v>1</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>country:DE-HH:national</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG80" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL80" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP80" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
-      <c r="AT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV80" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA80" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB80" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC80" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>DE-MV</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Mecklenburg-Vorpommern, Germany</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N81" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" t="n">
-        <v>1</v>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>country:DE-MV:national</t>
-        </is>
-      </c>
-      <c r="AD81" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG81" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL81" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP81" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
-      <c r="AT81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV81" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA81" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB81" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC81" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>DE-NI</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Niedersachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" t="n">
-        <v>1</v>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>country:DE-NI:national</t>
-        </is>
-      </c>
-      <c r="AD82" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG82" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP82" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
-      <c r="AT82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV82" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA82" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB82" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC82" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>DE-NW</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Nordrhein-Westfalen, Germany</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N83" t="n">
-        <v>1</v>
-      </c>
-      <c r="O83" t="n">
-        <v>1</v>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>country:DE-NW:national</t>
-        </is>
-      </c>
-      <c r="AD83" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG83" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL83" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP83" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
-      <c r="AT83" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV83" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA83" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB83" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC83" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>DE-RP</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Rheinland-Pfalz, Germany</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N84" t="n">
-        <v>1</v>
-      </c>
-      <c r="O84" t="n">
-        <v>1</v>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>country:DE-RP:national</t>
-        </is>
-      </c>
-      <c r="AD84" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE84" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG84" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP84" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
-      <c r="AT84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV84" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA84" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB84" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC84" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>DE-SH</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Schleswig-Holstein, Germany</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N85" t="n">
-        <v>1</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1</v>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>country:DE-SH:national</t>
-        </is>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL85" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP85" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
-      <c r="AT85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV85" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA85" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB85" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC85" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>DE-SL</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Saarland, Germany</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N86" t="n">
-        <v>1</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1</v>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>country:DE-SL:national</t>
-        </is>
-      </c>
-      <c r="AD86" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG86" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL86" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP86" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
-      <c r="AT86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV86" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA86" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB86" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC86" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>1</v>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>country:DE-SN:national</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL87" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP87" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
-      <c r="AT87" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV87" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA87" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB87" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC87" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>DE-ST</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Sachsen-Anhalt, Germany</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N88" t="n">
-        <v>1</v>
-      </c>
-      <c r="O88" t="n">
-        <v>1</v>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>country:DE-ST:national</t>
-        </is>
-      </c>
-      <c r="AD88" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG88" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL88" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP88" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
-      <c r="AT88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV88" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA88" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB88" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC88" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>DE-TH</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Thüringen, Germany</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N89" t="n">
-        <v>1</v>
-      </c>
-      <c r="O89" t="n">
-        <v>1</v>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>country:DE-TH:national</t>
-        </is>
-      </c>
-      <c r="AD89" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE89" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG89" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL89" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP89" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
-      <c r="AT89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV89" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA89" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB89" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC89" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>2004-07-01</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>2004-07</t>
-        </is>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP90" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
-      <c r="AT90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV90" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA90" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB90" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC90" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>2004-08-01</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>2004-08</t>
-        </is>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP91" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
-      <c r="AT91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV91" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA91" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB91" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC91" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>2004-09-01</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>2004-09</t>
-        </is>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP92" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
-      <c r="AT92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV92" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA92" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB92" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC92" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>2004-10-01</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>2004-10</t>
-        </is>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP93" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
-      <c r="AT93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV93" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA93" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB93" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC93" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>2004-11-01</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>2004-11</t>
-        </is>
-      </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP94" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
-      <c r="AT94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV94" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA94" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB94" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC94" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>2004-12-01</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>2004-12</t>
-        </is>
-      </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP95" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
-      <c r="AT95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV95" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA95" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB95" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC95" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -17815,7 +11235,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -17825,7 +11245,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -17845,7 +11265,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -17877,7 +11297,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d145/2000-2004.xlsx
+++ b/diseases/d145/2000-2004.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,22 +921,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,22 +1059,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,22 +1197,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,22 +1335,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,22 +1473,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,22 +1611,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,22 +1749,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,22 +1887,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,22 +2025,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,22 +2163,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,22 +2301,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,22 +2439,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2760,11 +2565,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2777,22 +2577,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2913,11 +2703,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2930,22 +2715,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3066,11 +2841,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3083,22 +2853,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3219,11 +2979,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3236,22 +2991,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3372,11 +3117,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3389,22 +3129,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3525,11 +3255,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3542,22 +3267,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3678,11 +3393,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3695,22 +3405,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3831,11 +3531,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3848,22 +3543,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3984,11 +3669,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4001,22 +3681,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4137,11 +3807,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4154,22 +3819,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4290,11 +3945,6 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4307,22 +3957,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4443,11 +4083,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4460,22 +4095,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4596,11 +4221,6 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4613,22 +4233,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4749,11 +4359,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4766,22 +4371,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4902,11 +4497,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4919,22 +4509,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5000,17 +4580,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE-NW</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Nordrhein-Westfalen, Germany</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5049,126 +4629,34 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="P30" t="n">
-        <v>1</v>
-      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN30" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
         <v>1</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -5181,12 +4669,12 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -5201,12 +4689,12 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5238,12 +4726,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DE-NW</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5268,101 +4756,83 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5389,17 +4859,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DE-NW</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5424,179 +4894,83 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2002-04-15</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>country:DE-NW:national</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN32" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5658,12 +5032,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5678,11 +5052,6 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5695,22 +5064,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5811,12 +5170,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5831,11 +5190,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5848,22 +5202,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5964,12 +5308,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5984,11 +5328,6 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6001,22 +5340,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6117,12 +5446,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6137,11 +5466,6 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6154,22 +5478,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6270,12 +5584,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6290,11 +5604,6 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6307,22 +5616,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6423,12 +5722,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6443,11 +5742,6 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6460,22 +5754,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6576,12 +5860,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6596,11 +5880,6 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6613,22 +5892,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6729,12 +5998,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6749,11 +6018,6 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6766,22 +6030,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6882,12 +6136,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6902,11 +6156,6 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6919,22 +6168,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7035,12 +6274,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -7055,11 +6294,6 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7072,22 +6306,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7188,12 +6412,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7208,11 +6432,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7225,22 +6444,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7341,12 +6550,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7361,11 +6570,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7378,22 +6582,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7494,12 +6688,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7514,11 +6708,6 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7531,22 +6720,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7647,12 +6826,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7667,11 +6846,6 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7684,22 +6858,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7800,12 +6964,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7820,11 +6984,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7837,22 +6996,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7953,12 +7102,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7973,11 +7122,6 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7990,22 +7134,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8106,12 +7240,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8126,11 +7260,6 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8143,22 +7272,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8259,12 +7378,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -8279,11 +7398,6 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8296,22 +7410,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8412,12 +7516,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8432,11 +7536,6 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8449,22 +7548,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8565,12 +7654,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8585,11 +7674,6 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8602,22 +7686,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8718,12 +7792,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -8738,11 +7812,6 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8755,22 +7824,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8871,12 +7930,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -8891,11 +7950,6 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8908,22 +7962,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9024,12 +8068,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -9044,11 +8088,6 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9061,22 +8100,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9177,12 +8206,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -9197,11 +8226,6 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9214,22 +8238,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9300,12 +8314,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9330,98 +8344,86 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-06-07</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9483,12 +8485,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -9503,11 +8505,6 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9520,22 +8517,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9601,17 +8588,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9636,178 +8623,83 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2004-06-07</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
-        </is>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN59" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9839,12 +8731,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9869,101 +8761,83 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2004-06-07</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9990,17 +8864,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -10025,179 +8899,83 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2004-06-07</t>
+          <t>2004-10-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>l-user-ckfallfieber</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>Läuserückfallfieber</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>country:DE-BY:national</t>
-        </is>
-      </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL61" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN61" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10259,12 +9037,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -10279,11 +9057,6 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10296,22 +9069,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10412,12 +9175,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-12-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-12</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -10432,11 +9195,6 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10449,23 +9207,13 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV63" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -10502,618 +9250,6 @@
         </is>
       </c>
       <c r="BC63" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>2004-09-01</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>2004-09</t>
-        </is>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP64" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
-      <c r="AT64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV64" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA64" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB64" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC64" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>2004-10-01</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>2004-10</t>
-        </is>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP65" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr"/>
-      <c r="AT65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV65" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA65" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB65" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC65" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>2004-11-01</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>2004-11</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP66" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
-      <c r="AT66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV66" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA66" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB66" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC66" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>relapsing-fever</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>D145</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Relapsing fever</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>回归热</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>2004-12-01</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>2004-12</t>
-        </is>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP67" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
-      <c r="AT67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV67" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA67" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB67" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC67" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -11245,7 +9381,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -11265,7 +9401,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -11275,7 +9411,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d145/2000-2004.xlsx
+++ b/diseases/d145/2000-2004.xlsx
@@ -4580,17 +4580,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DE-NW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4629,34 +4629,126 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN30" t="b">
+        <v>0</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>1</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -4669,12 +4761,12 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -4689,12 +4781,12 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4818,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-NW</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Nordrhein-Westfalen, Germany</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4756,83 +4848,101 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-04-15</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4859,17 +4969,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-NW</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Nordrhein-Westfalen, Germany</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4894,83 +5004,179 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-04-15</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>l-user-ckfallfieber</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Läuserückfallfieber</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>country:DE-NW:national</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN32" t="b">
+        <v>1</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5238,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5170,12 +5376,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5308,12 +5514,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5446,12 +5652,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5584,12 +5790,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -5722,12 +5928,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -5860,12 +6066,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -5998,12 +6204,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6136,12 +6342,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6274,12 +6480,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6412,12 +6618,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6550,12 +6756,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -6688,12 +6894,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -6826,12 +7032,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -6964,12 +7170,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7102,12 +7308,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7240,12 +7446,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7378,12 +7584,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -7516,12 +7722,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -7654,12 +7860,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -7792,12 +7998,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -7930,12 +8136,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -8068,12 +8274,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -8206,12 +8412,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -8314,12 +8520,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8344,33 +8550,34 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2004-06-07</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
@@ -8378,52 +8585,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
-        </is>
-      </c>
+      <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8485,12 +8688,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -8588,17 +8791,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8623,83 +8826,178 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-06-07</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>sha256:e7e831a24f7081a69c283c5e6fd6cba2bd8260a18e4b2660164d2ff018ee6150</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
+        <v>0</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -8731,12 +9029,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8761,83 +9059,101 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-06-07</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8864,17 +9180,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8899,83 +9215,179 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-06-07</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>l-user-ckfallfieber</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Läuserückfallfieber</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>country:DE-BY:national</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN61" t="b">
+        <v>1</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7b2b87dcdb1a68b36ad6696b745d</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9449,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -9175,12 +9587,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -9250,6 +9662,558 @@
         </is>
       </c>
       <c r="BC63" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>relapsing-fever</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>relapsing-fever</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>relapsing-fever</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>relapsing-fever</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -9381,7 +10345,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -9401,7 +10365,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -9411,7 +10375,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d145/2000-2004.xlsx
+++ b/diseases/d145/2000-2004.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -909,6 +924,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -921,12 +941,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1047,6 +1077,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1059,12 +1094,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1185,6 +1230,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1197,12 +1247,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1323,6 +1383,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1335,12 +1400,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1461,6 +1536,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1473,12 +1553,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1599,6 +1689,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1611,12 +1706,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1737,6 +1842,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1749,12 +1859,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1875,6 +1995,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1887,12 +2012,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2013,6 +2148,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2025,12 +2165,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2151,6 +2301,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2163,12 +2318,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2289,6 +2454,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2301,12 +2471,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2427,6 +2607,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2439,12 +2624,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2565,6 +2760,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2577,12 +2777,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2703,6 +2913,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2715,12 +2930,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2841,6 +3066,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2853,12 +3083,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2979,6 +3219,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2991,12 +3236,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3117,6 +3372,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3129,12 +3389,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3255,6 +3525,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3267,12 +3542,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3393,6 +3678,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3405,12 +3695,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3531,6 +3831,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3543,12 +3848,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3669,6 +3984,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3681,12 +4001,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3807,6 +4137,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3819,12 +4154,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -3945,6 +4290,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3957,12 +4307,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4083,6 +4443,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4095,12 +4460,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4221,6 +4596,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4233,12 +4613,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4359,6 +4749,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4371,12 +4766,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4497,6 +4902,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4509,12 +4919,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5258,6 +5678,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5270,12 +5695,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5396,6 +5831,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5408,12 +5848,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5534,6 +5984,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5546,12 +6001,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5672,6 +6137,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5684,12 +6154,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5810,6 +6290,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5822,12 +6307,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5948,6 +6443,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5960,12 +6460,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6086,6 +6596,11 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6098,12 +6613,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6224,6 +6749,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6236,12 +6766,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6362,6 +6902,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6374,12 +6919,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6500,6 +7055,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6512,12 +7072,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6638,6 +7208,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6650,12 +7225,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6776,6 +7361,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6788,12 +7378,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6914,6 +7514,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6926,12 +7531,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7052,6 +7667,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7064,12 +7684,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7190,6 +7820,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7202,12 +7837,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7328,6 +7973,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7340,12 +7990,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7466,6 +8126,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7478,12 +8143,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7604,6 +8279,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7616,12 +8296,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7742,6 +8432,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7754,12 +8449,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7880,6 +8585,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7892,12 +8602,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8018,6 +8738,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8030,12 +8755,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8156,6 +8891,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8168,12 +8908,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8294,6 +9044,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8306,12 +9061,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8432,6 +9197,11 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8444,12 +9214,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8570,6 +9350,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8582,12 +9367,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8708,6 +9503,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8720,12 +9520,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9469,6 +10279,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9481,12 +10296,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9607,6 +10432,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9619,12 +10449,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9745,6 +10585,11 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9757,12 +10602,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -9883,6 +10738,11 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9895,12 +10755,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10021,6 +10891,11 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10033,12 +10908,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10159,6 +11044,11 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10171,12 +11061,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
